--- a/data/trans_orig/IP07_A11_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP07_A11_2023-Estudios-trans_orig.xlsx
@@ -535,13 +535,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de tener problemas para dormir, percibida por el adulto en 2023 (tasa de respuesta: 99,9%)</t>
+          <t>Menores según la frecuencia de tener problemas para dormir, percibida por el/la adulto/a en 2023 (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>2871</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>710</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>7003</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>10,05%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>2,48%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>24,5%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2944</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>825</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6425</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>24,91%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>2871</t>
+          <t>2944</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>766</t>
+          <t>794</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6986</t>
+          <t>7275</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>13,83%</t>
         </is>
       </c>
     </row>
@@ -833,107 +833,107 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>962</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>3987</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>3,59%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>14,87%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>937</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>962</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>4395</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>3,4%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>4824</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>1,83%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>15,96%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>937</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>4325</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>1,67%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>9,17%</t>
         </is>
       </c>
     </row>
@@ -946,107 +946,107 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>717</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>801</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>3858</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>2,51%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>3761</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>3,11%</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>13,5%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>14,58%</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>801</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>3614</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>1,52%</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>717</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>3731</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>1,28%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,87%</t>
         </is>
       </c>
     </row>
@@ -1059,72 +1059,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2411</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>644</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>5885</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>8,99%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>2,4%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>21,95%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>1630</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>378</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>5210</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>5,7%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>1,32%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>18,23%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2479</t>
+          <t>1607</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>692</t>
+          <t>321</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6365</t>
+          <t>4936</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>19,14%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>4109</t>
+          <t>4018</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1848</t>
+          <t>1595</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8928</t>
+          <t>8784</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>16,7%</t>
         </is>
       </c>
     </row>
@@ -1172,72 +1172,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>23440</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>19479</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>25708</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>87,42%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>72,65%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>95,88%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>23364</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>18693</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>26254</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>81,74%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>65,4%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>91,85%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>24119</t>
+          <t>20441</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>20115</t>
+          <t>15825</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>26350</t>
+          <t>23102</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>87,59%</t>
+          <t>79,25%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>73,05%</t>
+          <t>61,35%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>89,57%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>47481</t>
+          <t>43880</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>41993</t>
+          <t>38635</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>51406</t>
+          <t>47829</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>84,61%</t>
+          <t>83,41%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>74,83%</t>
+          <t>73,44%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,61%</t>
+          <t>90,92%</t>
         </is>
       </c>
     </row>
@@ -1285,57 +1285,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>26813</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>26813</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>26813</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>34</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>28582</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>28582</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>28582</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>27535</t>
+          <t>25793</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>27535</t>
+          <t>25793</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>27535</t>
+          <t>25793</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>56116</t>
+          <t>52605</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>56116</t>
+          <t>52605</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>56116</t>
+          <t>52605</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1402,72 +1402,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>10983</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>6034</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>20714</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>3,71%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>2,04%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>6,99%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>5490</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>2268</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>11370</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>2,11%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,87%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>4,38%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>11058</t>
+          <t>6037</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5757</t>
+          <t>2755</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>19239</t>
+          <t>11773</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>16548</t>
+          <t>17020</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10428</t>
+          <t>10535</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>26986</t>
+          <t>27498</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>5,08%</t>
         </is>
       </c>
     </row>
@@ -1515,72 +1515,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>2560</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>584</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>6362</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0,86%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0,2%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>2,15%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>4755</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>1962</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>10075</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>1,83%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>0,76%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>3,88%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2264</t>
+          <t>5006</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>582</t>
+          <t>1887</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5995</t>
+          <t>10271</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>7019</t>
+          <t>7566</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>3561</t>
+          <t>3983</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>12428</t>
+          <t>13670</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,52%</t>
         </is>
       </c>
     </row>
@@ -1628,72 +1628,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>10811</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>4733</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>28302</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>3,65%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>1,6%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>9,55%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>6295</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>2422</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>12019</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>2,42%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0,93%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>4,63%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>15515</t>
+          <t>6688</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>5095</t>
+          <t>3203</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>36705</t>
+          <t>13810</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>21810</t>
+          <t>17499</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>11374</t>
+          <t>10254</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>45490</t>
+          <t>36651</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>6,76%</t>
         </is>
       </c>
     </row>
@@ -1741,72 +1741,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>35497</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>25332</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>47311</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>11,98%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>8,55%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>15,96%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>16489</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>9441</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>24960</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>6,35%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>3,63%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>9,61%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>34770</t>
+          <t>17764</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>25467</t>
+          <t>11622</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>45679</t>
+          <t>27023</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>51259</t>
+          <t>53261</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>39033</t>
+          <t>41173</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>65413</t>
+          <t>66486</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>12,27%</t>
         </is>
       </c>
     </row>
@@ -1854,72 +1854,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>265</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>236547</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>220267</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>249835</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>79,81%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>74,31%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>84,29%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>282</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>226760</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>214772</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>238675</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>87,29%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>82,67%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>91,87%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>265</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>245638</t>
+          <t>209918</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>224182</t>
+          <t>198863</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>261333</t>
+          <t>218582</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>79,43%</t>
+          <t>85,54%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>72,49%</t>
+          <t>81,03%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>84,51%</t>
+          <t>89,07%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>472399</t>
+          <t>446465</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>451239</t>
+          <t>426451</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>490252</t>
+          <t>463409</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>83,02%</t>
+          <t>82,4%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>79,3%</t>
+          <t>78,71%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,15%</t>
+          <t>85,53%</t>
         </is>
       </c>
     </row>
@@ -1967,57 +1967,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>334</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>296398</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>296398</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>296398</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>327</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>259789</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>259789</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>259789</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>334</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>309246</t>
+          <t>245413</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>309246</t>
+          <t>245413</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>309246</t>
+          <t>245413</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>569035</t>
+          <t>541811</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>569035</t>
+          <t>541811</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>569035</t>
+          <t>541811</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2084,72 +2084,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>4514</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1942</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>10437</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>4,66%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>2,01%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>10,78%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>2927</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>795</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>7068</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>3,62%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0,98%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>8,75%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>4398</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1526</t>
+          <t>880</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10356</t>
+          <t>8282</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>7325</t>
+          <t>7531</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3872</t>
+          <t>4195</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>14046</t>
+          <t>14559</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>8,04%</t>
         </is>
       </c>
     </row>
@@ -2202,7 +2202,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>794</t>
+          <t>665</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -2212,12 +2212,12 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3935</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -2227,7 +2227,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,7 +2237,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>750</t>
+          <t>864</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -2247,12 +2247,12 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4287</t>
+          <t>4419</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1544</t>
+          <t>1528</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5229</t>
+          <t>5041</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,78%</t>
         </is>
       </c>
     </row>
@@ -2310,72 +2310,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>6883</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>2668</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>15526</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>7,11%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>2,76%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>16,04%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>3794</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>1300</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>9127</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>3956</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>1372</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>8687</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>4,7%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>1,61%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>11,3%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>6726</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>2590</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>12784</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>6,53%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>10520</t>
+          <t>10838</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>5229</t>
+          <t>5400</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>18305</t>
+          <t>18981</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>10,49%</t>
         </is>
       </c>
     </row>
@@ -2423,72 +2423,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>6429</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>3063</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>11658</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>6,64%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>3,17%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>12,05%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>4609</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>9087</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>5,71%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>2,51%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>11,25%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>6895</t>
+          <t>4942</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3027</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>13021</t>
+          <t>10784</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>11504</t>
+          <t>11371</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>6057</t>
+          <t>6600</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>18169</t>
+          <t>18473</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>10,2%</t>
         </is>
       </c>
     </row>
@@ -2536,72 +2536,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>78282</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>70005</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>84717</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>80,89%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>72,34%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>87,54%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>98</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>68657</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>62084</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>73639</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>84,99%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>76,85%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>91,16%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>84174</t>
+          <t>71470</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>75188</t>
+          <t>64168</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>90322</t>
+          <t>76337</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>81,77%</t>
+          <t>84,83%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>73,04%</t>
+          <t>76,17%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>87,74%</t>
+          <t>90,61%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>152830</t>
+          <t>149752</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>142367</t>
+          <t>139636</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>161805</t>
+          <t>158666</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>83,18%</t>
+          <t>82,73%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>77,49%</t>
+          <t>77,14%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>88,07%</t>
+          <t>87,65%</t>
         </is>
       </c>
     </row>
@@ -2649,57 +2649,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>96773</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>96773</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>96773</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>114</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>80781</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>80781</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>80781</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>102943</t>
+          <t>84248</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>102943</t>
+          <t>84248</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>102943</t>
+          <t>84248</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>183724</t>
+          <t>181021</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>183724</t>
+          <t>181021</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>183724</t>
+          <t>181021</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2766,72 +2766,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>15497</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>9591</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>25579</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>3,69%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>2,28%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>6,09%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>11289</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>5896</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>18260</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>3,06%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>1,6%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>4,95%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>15456</t>
+          <t>11999</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>9163</t>
+          <t>6983</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>25541</t>
+          <t>19997</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>26745</t>
+          <t>27495</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>17465</t>
+          <t>19375</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>37984</t>
+          <t>39966</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>5,15%</t>
         </is>
       </c>
     </row>
@@ -2879,72 +2879,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>4187</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>1507</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>9035</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>1,0%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>0,36%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>2,15%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>5549</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>2036</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>10229</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>1,5%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>0,55%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>2,77%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3952</t>
+          <t>5870</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1484</t>
+          <t>2705</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>8748</t>
+          <t>11782</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,32 +2954,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>9500</t>
+          <t>10057</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5522</t>
+          <t>5763</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>17478</t>
+          <t>16981</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,19%</t>
         </is>
       </c>
     </row>
@@ -2992,72 +2992,72 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>17694</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>9440</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>31362</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>4,21%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>2,25%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>7,47%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>10806</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>6363</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>17662</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>2,93%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>1,72%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>4,78%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>22241</t>
+          <t>11444</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>11483</t>
+          <t>6884</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>47243</t>
+          <t>19440</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,32 +3067,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>33047</t>
+          <t>29139</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>20779</t>
+          <t>19354</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>57408</t>
+          <t>45246</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>5,83%</t>
         </is>
       </c>
     </row>
@@ -3105,72 +3105,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>44337</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>33724</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>58156</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>10,56%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>8,03%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>13,85%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>22728</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>15577</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>32350</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>6,16%</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>4,22%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>8,76%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>44144</t>
+          <t>24312</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>33080</t>
+          <t>16402</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>58709</t>
+          <t>33975</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>66873</t>
+          <t>68650</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>52815</t>
+          <t>54405</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>81402</t>
+          <t>82889</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>10,69%</t>
         </is>
       </c>
     </row>
@@ -3218,72 +3218,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>393</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>338269</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>320413</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>352690</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>80,54%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>76,29%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>83,98%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>406</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>318780</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>306785</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>332663</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>86,35%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>83,11%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>90,12%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>393</t>
-        </is>
-      </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>353931</t>
+          <t>301828</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>332203</t>
+          <t>288634</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>370907</t>
+          <t>313203</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>80,49%</t>
+          <t>84,91%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>75,55%</t>
+          <t>81,2%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>84,35%</t>
+          <t>88,11%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>672711</t>
+          <t>640096</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>647219</t>
+          <t>619358</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>695108</t>
+          <t>660123</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>83,17%</t>
+          <t>82,55%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>80,01%</t>
+          <t>79,87%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>85,94%</t>
+          <t>85,13%</t>
         </is>
       </c>
     </row>
@@ -3331,57 +3331,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>489</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>419984</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>419984</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>419984</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>475</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>369151</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>369151</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>369151</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>489</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>439724</t>
+          <t>355453</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>439724</t>
+          <t>355453</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>439724</t>
+          <t>355453</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>808876</t>
+          <t>775437</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>808876</t>
+          <t>775437</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>808876</t>
+          <t>775437</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
